--- a/grupos/3ASV - Estadisticos 20241.xlsx
+++ b/grupos/3ASV - Estadisticos 20241.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="201" uniqueCount="78">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="196" uniqueCount="78">
   <si>
     <t>Materia</t>
   </si>
@@ -173,18 +173,18 @@
     <t>CONTRERAS</t>
   </si>
   <si>
+    <t>PEREZ</t>
+  </si>
+  <si>
+    <t>BASILIO</t>
+  </si>
+  <si>
+    <t>BERNABE</t>
+  </si>
+  <si>
     <t>FLORES</t>
   </si>
   <si>
-    <t>PEREZ</t>
-  </si>
-  <si>
-    <t>BASILIO</t>
-  </si>
-  <si>
-    <t>BERNABE</t>
-  </si>
-  <si>
     <t>MARCELINO</t>
   </si>
   <si>
@@ -203,18 +203,18 @@
     <t>MARROQUIN</t>
   </si>
   <si>
+    <t>RIOS</t>
+  </si>
+  <si>
+    <t>SANCHEZ</t>
+  </si>
+  <si>
+    <t>ROMERO</t>
+  </si>
+  <si>
     <t>TINOCO</t>
   </si>
   <si>
-    <t>RIOS</t>
-  </si>
-  <si>
-    <t>SANCHEZ</t>
-  </si>
-  <si>
-    <t>ROMERO</t>
-  </si>
-  <si>
     <t>RUIZ</t>
   </si>
   <si>
@@ -233,16 +233,16 @@
     <t>CRISTIAN</t>
   </si>
   <si>
+    <t>NOHEMI ANGELICA</t>
+  </si>
+  <si>
+    <t>CLARA LIZBETH</t>
+  </si>
+  <si>
+    <t>HEIDI KESEI</t>
+  </si>
+  <si>
     <t>JULIO ALBERTO</t>
-  </si>
-  <si>
-    <t>NOHEMI ANGELICA</t>
-  </si>
-  <si>
-    <t>CLARA LIZBETH</t>
-  </si>
-  <si>
-    <t>HEIDI KESEI</t>
   </si>
   <si>
     <t>GIANCARLO</t>
@@ -797,10 +797,10 @@
         <v>10</v>
       </c>
       <c r="J4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K4">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L4">
         <v>-1</v>
@@ -809,16 +809,16 @@
         <v>-1</v>
       </c>
       <c r="N4">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O4">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P4">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R4">
         <v>-1</v>
@@ -845,10 +845,10 @@
         <v>-1</v>
       </c>
       <c r="Z4">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AA4">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AB4">
         <v>5</v>
@@ -860,7 +860,7 @@
         <v>7</v>
       </c>
       <c r="AE4">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AF4">
         <v>8</v>
@@ -898,10 +898,10 @@
         <v>10</v>
       </c>
       <c r="J5">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K5">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L5">
         <v>-1</v>
@@ -910,16 +910,16 @@
         <v>-1</v>
       </c>
       <c r="N5">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O5">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P5">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q5">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R5">
         <v>-1</v>
@@ -958,7 +958,7 @@
         <v>10</v>
       </c>
       <c r="AD5">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AE5">
         <v>10</v>
@@ -999,10 +999,10 @@
         <v>10</v>
       </c>
       <c r="J6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L6">
         <v>-1</v>
@@ -1011,16 +1011,16 @@
         <v>-1</v>
       </c>
       <c r="N6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R6">
         <v>-1</v>
@@ -1100,10 +1100,10 @@
         <v>10</v>
       </c>
       <c r="J7">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K7">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L7">
         <v>-1</v>
@@ -1112,16 +1112,16 @@
         <v>-1</v>
       </c>
       <c r="N7">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O7">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P7">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q7">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R7">
         <v>-1</v>
@@ -1148,10 +1148,10 @@
         <v>-1</v>
       </c>
       <c r="Z7">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AA7">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AB7">
         <v>5</v>
@@ -1163,7 +1163,7 @@
         <v>7</v>
       </c>
       <c r="AE7">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AF7">
         <v>8</v>
@@ -1201,10 +1201,10 @@
         <v>10</v>
       </c>
       <c r="J8">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K8">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L8">
         <v>-1</v>
@@ -1213,16 +1213,16 @@
         <v>-1</v>
       </c>
       <c r="N8">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O8">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P8">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q8">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R8">
         <v>-1</v>
@@ -1249,7 +1249,7 @@
         <v>-1</v>
       </c>
       <c r="Z8">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AA8">
         <v>9</v>
@@ -1261,10 +1261,10 @@
         <v>8</v>
       </c>
       <c r="AD8">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AE8">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AF8">
         <v>10</v>
@@ -1302,10 +1302,10 @@
         <v>10</v>
       </c>
       <c r="J9">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K9">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L9">
         <v>-1</v>
@@ -1314,16 +1314,16 @@
         <v>-1</v>
       </c>
       <c r="N9">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O9">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P9">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q9">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R9">
         <v>-1</v>
@@ -1350,10 +1350,10 @@
         <v>-1</v>
       </c>
       <c r="Z9">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AA9">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AB9">
         <v>8</v>
@@ -1362,10 +1362,10 @@
         <v>8</v>
       </c>
       <c r="AD9">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AE9">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AF9">
         <v>10</v>
@@ -1403,10 +1403,10 @@
         <v>10</v>
       </c>
       <c r="J10">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K10">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L10">
         <v>-1</v>
@@ -1415,16 +1415,16 @@
         <v>-1</v>
       </c>
       <c r="N10">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O10">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P10">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q10">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R10">
         <v>-1</v>
@@ -1451,10 +1451,10 @@
         <v>-1</v>
       </c>
       <c r="Z10">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AA10">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AB10">
         <v>8</v>
@@ -1466,7 +1466,7 @@
         <v>7</v>
       </c>
       <c r="AE10">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AF10">
         <v>10</v>
@@ -1504,10 +1504,10 @@
         <v>10</v>
       </c>
       <c r="J11">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K11">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L11">
         <v>-1</v>
@@ -1516,16 +1516,16 @@
         <v>-1</v>
       </c>
       <c r="N11">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O11">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P11">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q11">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R11">
         <v>-1</v>
@@ -1552,7 +1552,7 @@
         <v>-1</v>
       </c>
       <c r="Z11">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AA11">
         <v>10</v>
@@ -1564,13 +1564,13 @@
         <v>10</v>
       </c>
       <c r="AD11">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AE11">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AF11">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AG11">
         <v>-1</v>
@@ -1605,10 +1605,10 @@
         <v>10</v>
       </c>
       <c r="J12">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K12">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L12">
         <v>-1</v>
@@ -1617,16 +1617,16 @@
         <v>-1</v>
       </c>
       <c r="N12">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O12">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P12">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q12">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R12">
         <v>-1</v>
@@ -1656,7 +1656,7 @@
         <v>7</v>
       </c>
       <c r="AA12">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AB12">
         <v>5</v>
@@ -1668,10 +1668,10 @@
         <v>9</v>
       </c>
       <c r="AE12">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AF12">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AG12">
         <v>-1</v>
@@ -1706,10 +1706,10 @@
         <v>10</v>
       </c>
       <c r="J13">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K13">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L13">
         <v>-1</v>
@@ -1718,16 +1718,16 @@
         <v>-1</v>
       </c>
       <c r="N13">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O13">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P13">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q13">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R13">
         <v>-1</v>
@@ -1956,10 +1956,10 @@
         <v>100</v>
       </c>
       <c r="O4">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="P4">
-        <v>97.09999999999999</v>
+        <v>92.90000000000001</v>
       </c>
       <c r="Q4">
         <v>100</v>
@@ -1980,10 +1980,10 @@
         <v>100</v>
       </c>
       <c r="W4">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="X4">
-        <v>97.09999999999999</v>
+        <v>92.90000000000001</v>
       </c>
       <c r="Y4">
         <v>100</v>
@@ -2175,7 +2175,7 @@
         <v>100</v>
       </c>
       <c r="K7">
-        <v>95.5</v>
+        <v>97.7</v>
       </c>
       <c r="L7">
         <v>100</v>
@@ -2184,13 +2184,13 @@
         <v>100</v>
       </c>
       <c r="N7">
-        <v>100</v>
+        <v>97.8</v>
       </c>
       <c r="O7">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="P7">
-        <v>97.09999999999999</v>
+        <v>92.90000000000001</v>
       </c>
       <c r="Q7">
         <v>100</v>
@@ -2199,7 +2199,7 @@
         <v>100</v>
       </c>
       <c r="S7">
-        <v>95.5</v>
+        <v>97.7</v>
       </c>
       <c r="T7">
         <v>100</v>
@@ -2208,13 +2208,13 @@
         <v>100</v>
       </c>
       <c r="V7">
-        <v>100</v>
+        <v>97.8</v>
       </c>
       <c r="W7">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="X7">
-        <v>97.09999999999999</v>
+        <v>92.90000000000001</v>
       </c>
       <c r="Y7">
         <v>100</v>
@@ -2329,7 +2329,7 @@
         <v>100</v>
       </c>
       <c r="K9">
-        <v>90.90000000000001</v>
+        <v>93.2</v>
       </c>
       <c r="L9">
         <v>100</v>
@@ -2338,7 +2338,7 @@
         <v>100</v>
       </c>
       <c r="N9">
-        <v>100</v>
+        <v>97.8</v>
       </c>
       <c r="O9">
         <v>100</v>
@@ -2353,7 +2353,7 @@
         <v>100</v>
       </c>
       <c r="S9">
-        <v>90.90000000000001</v>
+        <v>93.2</v>
       </c>
       <c r="T9">
         <v>100</v>
@@ -2362,7 +2362,7 @@
         <v>100</v>
       </c>
       <c r="V9">
-        <v>100</v>
+        <v>97.8</v>
       </c>
       <c r="W9">
         <v>100</v>
@@ -2406,7 +2406,7 @@
         <v>100</v>
       </c>
       <c r="K10">
-        <v>100</v>
+        <v>97.7</v>
       </c>
       <c r="L10">
         <v>100</v>
@@ -2421,7 +2421,7 @@
         <v>100</v>
       </c>
       <c r="P10">
-        <v>100</v>
+        <v>94.3</v>
       </c>
       <c r="Q10">
         <v>100</v>
@@ -2430,7 +2430,7 @@
         <v>100</v>
       </c>
       <c r="S10">
-        <v>100</v>
+        <v>97.7</v>
       </c>
       <c r="T10">
         <v>100</v>
@@ -2445,7 +2445,7 @@
         <v>100</v>
       </c>
       <c r="X10">
-        <v>100</v>
+        <v>94.3</v>
       </c>
       <c r="Y10">
         <v>100</v>
@@ -2483,7 +2483,7 @@
         <v>100</v>
       </c>
       <c r="K11">
-        <v>95.5</v>
+        <v>97.7</v>
       </c>
       <c r="L11">
         <v>100</v>
@@ -2498,7 +2498,7 @@
         <v>100</v>
       </c>
       <c r="P11">
-        <v>97.09999999999999</v>
+        <v>98.59999999999999</v>
       </c>
       <c r="Q11">
         <v>100</v>
@@ -2507,7 +2507,7 @@
         <v>100</v>
       </c>
       <c r="S11">
-        <v>95.5</v>
+        <v>97.7</v>
       </c>
       <c r="T11">
         <v>100</v>
@@ -2522,7 +2522,7 @@
         <v>100</v>
       </c>
       <c r="X11">
-        <v>97.09999999999999</v>
+        <v>98.59999999999999</v>
       </c>
       <c r="Y11">
         <v>100</v>
@@ -2572,7 +2572,7 @@
         <v>100</v>
       </c>
       <c r="O12">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="P12">
         <v>97.09999999999999</v>
@@ -2596,7 +2596,7 @@
         <v>100</v>
       </c>
       <c r="W12">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="X12">
         <v>97.09999999999999</v>
@@ -2637,7 +2637,7 @@
         <v>100</v>
       </c>
       <c r="K13">
-        <v>100</v>
+        <v>97.7</v>
       </c>
       <c r="L13">
         <v>100</v>
@@ -2652,7 +2652,7 @@
         <v>100</v>
       </c>
       <c r="P13">
-        <v>100</v>
+        <v>98.59999999999999</v>
       </c>
       <c r="Q13">
         <v>100</v>
@@ -2661,7 +2661,7 @@
         <v>100</v>
       </c>
       <c r="S13">
-        <v>100</v>
+        <v>97.7</v>
       </c>
       <c r="T13">
         <v>100</v>
@@ -2676,7 +2676,7 @@
         <v>100</v>
       </c>
       <c r="X13">
-        <v>100</v>
+        <v>98.59999999999999</v>
       </c>
       <c r="Y13">
         <v>100</v>
@@ -2806,19 +2806,19 @@
         <v>10</v>
       </c>
       <c r="D4">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F4" s="2">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="G4" s="2">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="H4">
-        <v>8</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="I4">
         <v>0</v>
@@ -2850,7 +2850,7 @@
         <v>0</v>
       </c>
       <c r="H5">
-        <v>8.800000000000001</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="I5">
         <v>0</v>
@@ -2946,7 +2946,7 @@
         <v>0</v>
       </c>
       <c r="H8">
-        <v>8.300000000000001</v>
+        <v>9</v>
       </c>
       <c r="I8">
         <v>0</v>
@@ -2978,7 +2978,7 @@
         <v>0</v>
       </c>
       <c r="H9">
-        <v>8.9</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="I9">
         <v>0</v>
@@ -3028,7 +3028,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G16"/>
+  <dimension ref="A1:G15"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -3198,7 +3198,7 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>23330051920290</v>
+        <v>23330051920303</v>
       </c>
       <c r="B8" t="s">
         <v>51</v>
@@ -3210,10 +3210,10 @@
         <v>71</v>
       </c>
       <c r="E8" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="F8" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="G8">
         <v>5</v>
@@ -3221,7 +3221,7 @@
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>23330051920290</v>
+        <v>23330051920303</v>
       </c>
       <c r="B9" t="s">
         <v>51</v>
@@ -3244,7 +3244,7 @@
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>23330051920303</v>
+        <v>23330051920287</v>
       </c>
       <c r="B10" t="s">
         <v>52</v>
@@ -3256,27 +3256,27 @@
         <v>72</v>
       </c>
       <c r="E10" t="s">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="F10" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="G10">
-        <v>5</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="11" spans="1:7">
       <c r="A11">
-        <v>23330051920303</v>
+        <v>23330051920288</v>
       </c>
       <c r="B11" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C11" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="D11" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="E11" t="s">
         <v>12</v>
@@ -3290,16 +3290,16 @@
     </row>
     <row r="12" spans="1:7">
       <c r="A12">
-        <v>23330051920287</v>
+        <v>23330051920290</v>
       </c>
       <c r="B12" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C12" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="D12" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="E12" t="s">
         <v>12</v>
@@ -3313,16 +3313,16 @@
     </row>
     <row r="13" spans="1:7">
       <c r="A13">
-        <v>23330051920288</v>
+        <v>23330051920300</v>
       </c>
       <c r="B13" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="C13" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="D13" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="E13" t="s">
         <v>12</v>
@@ -3336,16 +3336,16 @@
     </row>
     <row r="14" spans="1:7">
       <c r="A14">
-        <v>23330051920300</v>
+        <v>23330051920302</v>
       </c>
       <c r="B14" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="C14" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="D14" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="E14" t="s">
         <v>12</v>
@@ -3359,16 +3359,16 @@
     </row>
     <row r="15" spans="1:7">
       <c r="A15">
-        <v>23330051920302</v>
+        <v>23330051920304</v>
       </c>
       <c r="B15" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="C15" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="D15" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="E15" t="s">
         <v>12</v>
@@ -3377,29 +3377,6 @@
         <v>36</v>
       </c>
       <c r="G15">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7">
-      <c r="A16">
-        <v>23330051920304</v>
-      </c>
-      <c r="B16" t="s">
-        <v>57</v>
-      </c>
-      <c r="C16" t="s">
-        <v>67</v>
-      </c>
-      <c r="D16" t="s">
-        <v>77</v>
-      </c>
-      <c r="E16" t="s">
-        <v>12</v>
-      </c>
-      <c r="F16" t="s">
-        <v>36</v>
-      </c>
-      <c r="G16">
         <v>-1</v>
       </c>
     </row>

--- a/grupos/3ASV - Estadisticos 20241.xlsx
+++ b/grupos/3ASV - Estadisticos 20241.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="196" uniqueCount="78">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="186" uniqueCount="78">
   <si>
     <t>Materia</t>
   </si>
@@ -137,7 +137,7 @@
     <t>Muñoz Rivadeneyra Salvador</t>
   </si>
   <si>
-    <t>Hernández Mendoza Delfina</t>
+    <t>Breniz Camarillo Lysette</t>
   </si>
   <si>
     <t>Saucedo Rivalcoba Graciela</t>
@@ -164,24 +164,24 @@
     <t>Nombres</t>
   </si>
   <si>
+    <t>COCOTLE</t>
+  </si>
+  <si>
+    <t>PEREZ</t>
+  </si>
+  <si>
     <t>ANTONIO</t>
   </si>
   <si>
-    <t>COCOTLE</t>
+    <t>BASILIO</t>
+  </si>
+  <si>
+    <t>BERNABE</t>
   </si>
   <si>
     <t>CONTRERAS</t>
   </si>
   <si>
-    <t>PEREZ</t>
-  </si>
-  <si>
-    <t>BASILIO</t>
-  </si>
-  <si>
-    <t>BERNABE</t>
-  </si>
-  <si>
     <t>FLORES</t>
   </si>
   <si>
@@ -194,24 +194,24 @@
     <t>RAMOS</t>
   </si>
   <si>
+    <t>IXMATLAHUA</t>
+  </si>
+  <si>
+    <t>RIOS</t>
+  </si>
+  <si>
     <t>DIAZ</t>
   </si>
   <si>
-    <t>IXMATLAHUA</t>
+    <t>SANCHEZ</t>
+  </si>
+  <si>
+    <t>ROMERO</t>
   </si>
   <si>
     <t>MARROQUIN</t>
   </si>
   <si>
-    <t>RIOS</t>
-  </si>
-  <si>
-    <t>SANCHEZ</t>
-  </si>
-  <si>
-    <t>ROMERO</t>
-  </si>
-  <si>
     <t>TINOCO</t>
   </si>
   <si>
@@ -224,22 +224,22 @@
     <t>VILLEGAS</t>
   </si>
   <si>
+    <t>PAOLA</t>
+  </si>
+  <si>
+    <t>NOHEMI ANGELICA</t>
+  </si>
+  <si>
     <t>JOSUE</t>
   </si>
   <si>
-    <t>PAOLA</t>
+    <t>CLARA LIZBETH</t>
+  </si>
+  <si>
+    <t>HEIDI KESEI</t>
   </si>
   <si>
     <t>CRISTIAN</t>
-  </si>
-  <si>
-    <t>NOHEMI ANGELICA</t>
-  </si>
-  <si>
-    <t>CLARA LIZBETH</t>
-  </si>
-  <si>
-    <t>HEIDI KESEI</t>
   </si>
   <si>
     <t>JULIO ALBERTO</t>
@@ -803,10 +803,10 @@
         <v>9</v>
       </c>
       <c r="L4">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M4">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N4">
         <v>7</v>
@@ -851,7 +851,7 @@
         <v>9</v>
       </c>
       <c r="AB4">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AC4">
         <v>10</v>
@@ -904,10 +904,10 @@
         <v>10</v>
       </c>
       <c r="L5">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M5">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N5">
         <v>10</v>
@@ -1005,10 +1005,10 @@
         <v>10</v>
       </c>
       <c r="L6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N6">
         <v>10</v>
@@ -1106,10 +1106,10 @@
         <v>10</v>
       </c>
       <c r="L7">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M7">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N7">
         <v>7</v>
@@ -1157,7 +1157,7 @@
         <v>5</v>
       </c>
       <c r="AC7">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AD7">
         <v>7</v>
@@ -1207,10 +1207,10 @@
         <v>9</v>
       </c>
       <c r="L8">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M8">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N8">
         <v>7</v>
@@ -1255,10 +1255,10 @@
         <v>9</v>
       </c>
       <c r="AB8">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AC8">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AD8">
         <v>8</v>
@@ -1308,10 +1308,10 @@
         <v>9</v>
       </c>
       <c r="L9">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M9">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N9">
         <v>8</v>
@@ -1356,10 +1356,10 @@
         <v>9</v>
       </c>
       <c r="AB9">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AC9">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AD9">
         <v>7</v>
@@ -1409,10 +1409,10 @@
         <v>9</v>
       </c>
       <c r="L10">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M10">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N10">
         <v>6</v>
@@ -1460,7 +1460,7 @@
         <v>8</v>
       </c>
       <c r="AC10">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AD10">
         <v>7</v>
@@ -1510,10 +1510,10 @@
         <v>10</v>
       </c>
       <c r="L11">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M11">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N11">
         <v>9</v>
@@ -1558,7 +1558,7 @@
         <v>10</v>
       </c>
       <c r="AB11">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AC11">
         <v>10</v>
@@ -1611,10 +1611,10 @@
         <v>10</v>
       </c>
       <c r="L12">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M12">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N12">
         <v>8</v>
@@ -1712,10 +1712,10 @@
         <v>10</v>
       </c>
       <c r="L13">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M13">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N13">
         <v>9</v>
@@ -1760,7 +1760,7 @@
         <v>10</v>
       </c>
       <c r="AB13">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AC13">
         <v>10</v>
@@ -2178,10 +2178,10 @@
         <v>97.7</v>
       </c>
       <c r="L7">
-        <v>100</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="M7">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="N7">
         <v>97.8</v>
@@ -2202,10 +2202,10 @@
         <v>97.7</v>
       </c>
       <c r="T7">
-        <v>100</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="U7">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="V7">
         <v>97.8</v>
@@ -2332,7 +2332,7 @@
         <v>93.2</v>
       </c>
       <c r="L9">
-        <v>100</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="M9">
         <v>100</v>
@@ -2356,7 +2356,7 @@
         <v>93.2</v>
       </c>
       <c r="T9">
-        <v>100</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="U9">
         <v>100</v>
@@ -2409,7 +2409,7 @@
         <v>97.7</v>
       </c>
       <c r="L10">
-        <v>100</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="M10">
         <v>100</v>
@@ -2433,7 +2433,7 @@
         <v>97.7</v>
       </c>
       <c r="T10">
-        <v>100</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="U10">
         <v>100</v>
@@ -2563,7 +2563,7 @@
         <v>95.5</v>
       </c>
       <c r="L12">
-        <v>81.3</v>
+        <v>87.5</v>
       </c>
       <c r="M12">
         <v>100</v>
@@ -2587,7 +2587,7 @@
         <v>95.5</v>
       </c>
       <c r="T12">
-        <v>81.3</v>
+        <v>87.5</v>
       </c>
       <c r="U12">
         <v>100</v>
@@ -2774,19 +2774,19 @@
         <v>10</v>
       </c>
       <c r="D3">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E3">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F3" s="2">
-        <v>60</v>
+        <v>80</v>
       </c>
       <c r="G3" s="2">
-        <v>40</v>
+        <v>20</v>
       </c>
       <c r="H3">
-        <v>7.3</v>
+        <v>7.8</v>
       </c>
       <c r="I3">
         <v>0</v>
@@ -2882,7 +2882,7 @@
         <v>0</v>
       </c>
       <c r="H6">
-        <v>9.199999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="I6">
         <v>0</v>
@@ -3028,7 +3028,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G15"/>
+  <dimension ref="A1:G13"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -3060,7 +3060,7 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>23330051920319</v>
+        <v>23330051920339</v>
       </c>
       <c r="B2" t="s">
         <v>48</v>
@@ -3083,7 +3083,7 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>23330051920319</v>
+        <v>23330051920339</v>
       </c>
       <c r="B3" t="s">
         <v>48</v>
@@ -3106,7 +3106,7 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>23330051920339</v>
+        <v>23330051920303</v>
       </c>
       <c r="B4" t="s">
         <v>49</v>
@@ -3129,7 +3129,7 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>23330051920339</v>
+        <v>23330051920303</v>
       </c>
       <c r="B5" t="s">
         <v>49</v>
@@ -3152,7 +3152,7 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>23330051920289</v>
+        <v>23330051920319</v>
       </c>
       <c r="B6" t="s">
         <v>50</v>
@@ -3164,27 +3164,27 @@
         <v>70</v>
       </c>
       <c r="E6" t="s">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="F6" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="G6">
-        <v>5</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>23330051920289</v>
+        <v>23330051920287</v>
       </c>
       <c r="B7" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="C7" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="D7" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="E7" t="s">
         <v>12</v>
@@ -3198,39 +3198,39 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>23330051920303</v>
+        <v>23330051920288</v>
       </c>
       <c r="B8" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="C8" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="D8" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="E8" t="s">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="F8" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="G8">
-        <v>5</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>23330051920303</v>
+        <v>23330051920289</v>
       </c>
       <c r="B9" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="C9" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="D9" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="E9" t="s">
         <v>12</v>
@@ -3244,16 +3244,16 @@
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>23330051920287</v>
+        <v>23330051920290</v>
       </c>
       <c r="B10" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="C10" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="D10" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="E10" t="s">
         <v>12</v>
@@ -3267,16 +3267,16 @@
     </row>
     <row r="11" spans="1:7">
       <c r="A11">
-        <v>23330051920288</v>
+        <v>23330051920300</v>
       </c>
       <c r="B11" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="C11" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="D11" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="E11" t="s">
         <v>12</v>
@@ -3290,16 +3290,16 @@
     </row>
     <row r="12" spans="1:7">
       <c r="A12">
-        <v>23330051920290</v>
+        <v>23330051920302</v>
       </c>
       <c r="B12" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="C12" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="D12" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="E12" t="s">
         <v>12</v>
@@ -3313,16 +3313,16 @@
     </row>
     <row r="13" spans="1:7">
       <c r="A13">
-        <v>23330051920300</v>
+        <v>23330051920304</v>
       </c>
       <c r="B13" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="C13" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="D13" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="E13" t="s">
         <v>12</v>
@@ -3331,52 +3331,6 @@
         <v>36</v>
       </c>
       <c r="G13">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7">
-      <c r="A14">
-        <v>23330051920302</v>
-      </c>
-      <c r="B14" t="s">
-        <v>56</v>
-      </c>
-      <c r="C14" t="s">
-        <v>66</v>
-      </c>
-      <c r="D14" t="s">
-        <v>76</v>
-      </c>
-      <c r="E14" t="s">
-        <v>12</v>
-      </c>
-      <c r="F14" t="s">
-        <v>36</v>
-      </c>
-      <c r="G14">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7">
-      <c r="A15">
-        <v>23330051920304</v>
-      </c>
-      <c r="B15" t="s">
-        <v>57</v>
-      </c>
-      <c r="C15" t="s">
-        <v>67</v>
-      </c>
-      <c r="D15" t="s">
-        <v>77</v>
-      </c>
-      <c r="E15" t="s">
-        <v>12</v>
-      </c>
-      <c r="F15" t="s">
-        <v>36</v>
-      </c>
-      <c r="G15">
         <v>-1</v>
       </c>
     </row>

--- a/grupos/3ASV - Estadisticos 20241.xlsx
+++ b/grupos/3ASV - Estadisticos 20241.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="129" uniqueCount="54">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="119" uniqueCount="48">
   <si>
     <t>Materia</t>
   </si>
@@ -128,18 +128,18 @@
     <t>Recursos socioemocionales III</t>
   </si>
   <si>
+    <t>Muñoz Rivadeneyra Salvador</t>
+  </si>
+  <si>
+    <t>Breniz Camarillo Lysette</t>
+  </si>
+  <si>
+    <t>Saucedo Rivalcoba Graciela</t>
+  </si>
+  <si>
     <t>Villanueva Morales Luis Arturo</t>
   </si>
   <si>
-    <t>Muñoz Rivadeneyra Salvador</t>
-  </si>
-  <si>
-    <t>Breniz Camarillo Lysette</t>
-  </si>
-  <si>
-    <t>Saucedo Rivalcoba Graciela</t>
-  </si>
-  <si>
     <t>Acevedo Rendón Ismael Arturo</t>
   </si>
   <si>
@@ -162,24 +162,6 @@
   </si>
   <si>
     <t>Nombres</t>
-  </si>
-  <si>
-    <t>COCOTLE</t>
-  </si>
-  <si>
-    <t>PEREZ</t>
-  </si>
-  <si>
-    <t>IXMATLAHUA</t>
-  </si>
-  <si>
-    <t>RIOS</t>
-  </si>
-  <si>
-    <t>PAOLA</t>
-  </si>
-  <si>
-    <t>NOHEMI ANGELICA</t>
   </si>
 </sst>
 </file>
@@ -733,19 +715,19 @@
         <v>-1</v>
       </c>
       <c r="R4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T4">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="U4">
         <v>-1</v>
       </c>
       <c r="V4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="W4">
         <v>10</v>
@@ -754,7 +736,7 @@
         <v>9</v>
       </c>
       <c r="Y4">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Z4">
         <v>10</v>
@@ -822,19 +804,19 @@
         <v>-1</v>
       </c>
       <c r="R5">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S5">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T5">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="U5">
         <v>-1</v>
       </c>
       <c r="V5">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="W5">
         <v>10</v>
@@ -911,19 +893,19 @@
         <v>-1</v>
       </c>
       <c r="R6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="U6">
         <v>-1</v>
       </c>
       <c r="V6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="W6">
         <v>10</v>
@@ -1000,19 +982,19 @@
         <v>-1</v>
       </c>
       <c r="R7">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S7">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T7">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="U7">
         <v>-1</v>
       </c>
       <c r="V7">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="W7">
         <v>9</v>
@@ -1021,7 +1003,7 @@
         <v>9</v>
       </c>
       <c r="Y7">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="Z7">
         <v>9</v>
@@ -1089,19 +1071,19 @@
         <v>-1</v>
       </c>
       <c r="R8">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S8">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T8">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="U8">
         <v>-1</v>
       </c>
       <c r="V8">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="W8">
         <v>9</v>
@@ -1110,7 +1092,7 @@
         <v>9</v>
       </c>
       <c r="Y8">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Z8">
         <v>9</v>
@@ -1178,19 +1160,19 @@
         <v>-1</v>
       </c>
       <c r="R9">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S9">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T9">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="U9">
         <v>-1</v>
       </c>
       <c r="V9">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="W9">
         <v>9</v>
@@ -1205,7 +1187,7 @@
         <v>9</v>
       </c>
       <c r="AA9">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AB9">
         <v>9</v>
@@ -1267,19 +1249,19 @@
         <v>-1</v>
       </c>
       <c r="R10">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S10">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T10">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="U10">
         <v>-1</v>
       </c>
       <c r="V10">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="W10">
         <v>9</v>
@@ -1288,7 +1270,7 @@
         <v>8</v>
       </c>
       <c r="Y10">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Z10">
         <v>9</v>
@@ -1356,19 +1338,19 @@
         <v>-1</v>
       </c>
       <c r="R11">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S11">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T11">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="U11">
         <v>-1</v>
       </c>
       <c r="V11">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="W11">
         <v>10</v>
@@ -1445,19 +1427,19 @@
         <v>-1</v>
       </c>
       <c r="R12">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S12">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T12">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="U12">
         <v>-1</v>
       </c>
       <c r="V12">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="W12">
         <v>7</v>
@@ -1466,13 +1448,13 @@
         <v>9</v>
       </c>
       <c r="Y12">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="Z12">
         <v>10</v>
       </c>
       <c r="AA12">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AB12">
         <v>7</v>
@@ -1534,19 +1516,19 @@
         <v>-1</v>
       </c>
       <c r="R13">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S13">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T13">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="U13">
         <v>-1</v>
       </c>
       <c r="V13">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="W13">
         <v>10</v>
@@ -1757,7 +1739,7 @@
         <v>98</v>
       </c>
       <c r="V4">
-        <v>92.90000000000001</v>
+        <v>90.2</v>
       </c>
     </row>
     <row r="5" spans="1:22">
@@ -1825,7 +1807,7 @@
         <v>100</v>
       </c>
       <c r="V5">
-        <v>100</v>
+        <v>96.40000000000001</v>
       </c>
     </row>
     <row r="6" spans="1:22">
@@ -1949,19 +1931,19 @@
         <v>97.7</v>
       </c>
       <c r="R7">
-        <v>96.90000000000001</v>
+        <v>97.90000000000001</v>
       </c>
       <c r="S7">
-        <v>97</v>
+        <v>97.90000000000001</v>
       </c>
       <c r="T7">
-        <v>97.8</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="U7">
         <v>98</v>
       </c>
       <c r="V7">
-        <v>92.90000000000001</v>
+        <v>92</v>
       </c>
     </row>
     <row r="8" spans="1:22">
@@ -2085,19 +2067,19 @@
         <v>93.2</v>
       </c>
       <c r="R9">
-        <v>96.90000000000001</v>
+        <v>97.90000000000001</v>
       </c>
       <c r="S9">
         <v>100</v>
       </c>
       <c r="T9">
-        <v>97.8</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="U9">
         <v>100</v>
       </c>
       <c r="V9">
-        <v>97.09999999999999</v>
+        <v>91.09999999999999</v>
       </c>
     </row>
     <row r="10" spans="1:22">
@@ -2153,7 +2135,7 @@
         <v>97.7</v>
       </c>
       <c r="R10">
-        <v>96.90000000000001</v>
+        <v>97.90000000000001</v>
       </c>
       <c r="S10">
         <v>100</v>
@@ -2165,7 +2147,7 @@
         <v>100</v>
       </c>
       <c r="V10">
-        <v>94.3</v>
+        <v>96.40000000000001</v>
       </c>
     </row>
     <row r="11" spans="1:22">
@@ -2233,7 +2215,7 @@
         <v>100</v>
       </c>
       <c r="V11">
-        <v>98.59999999999999</v>
+        <v>99.09999999999999</v>
       </c>
     </row>
     <row r="12" spans="1:22">
@@ -2289,7 +2271,7 @@
         <v>95.5</v>
       </c>
       <c r="R12">
-        <v>87.5</v>
+        <v>91.7</v>
       </c>
       <c r="S12">
         <v>100</v>
@@ -2301,7 +2283,7 @@
         <v>98</v>
       </c>
       <c r="V12">
-        <v>97.09999999999999</v>
+        <v>96.40000000000001</v>
       </c>
     </row>
     <row r="13" spans="1:22">
@@ -2369,7 +2351,7 @@
         <v>100</v>
       </c>
       <c r="V13">
-        <v>98.59999999999999</v>
+        <v>99.09999999999999</v>
       </c>
     </row>
   </sheetData>
@@ -2426,7 +2408,7 @@
     </row>
     <row r="2" spans="1:10">
       <c r="A2" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="B2" t="s">
         <v>36</v>
@@ -2435,19 +2417,19 @@
         <v>10</v>
       </c>
       <c r="D2">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E2">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F2" s="2">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="G2" s="2">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="H2">
-        <v>7.8</v>
+        <v>8.1</v>
       </c>
       <c r="I2">
         <v>0</v>
@@ -2458,7 +2440,7 @@
     </row>
     <row r="3" spans="1:10">
       <c r="A3" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="B3" t="s">
         <v>37</v>
@@ -2479,7 +2461,7 @@
         <v>0</v>
       </c>
       <c r="H3">
-        <v>8.300000000000001</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="I3">
         <v>0</v>
@@ -2490,7 +2472,7 @@
     </row>
     <row r="4" spans="1:10">
       <c r="A4" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="B4" t="s">
         <v>38</v>
@@ -2511,7 +2493,7 @@
         <v>0</v>
       </c>
       <c r="H4">
-        <v>9.300000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="I4">
         <v>0</v>
@@ -2522,7 +2504,7 @@
     </row>
     <row r="5" spans="1:10">
       <c r="A5" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B5" t="s">
         <v>39</v>
@@ -2543,7 +2525,7 @@
         <v>0</v>
       </c>
       <c r="H5">
-        <v>9.6</v>
+        <v>8.5</v>
       </c>
       <c r="I5">
         <v>0</v>
@@ -2709,7 +2691,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G3"/>
+  <dimension ref="A1:G1"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -2739,52 +2721,6 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:7">
-      <c r="A2">
-        <v>23330051920339</v>
-      </c>
-      <c r="B2" t="s">
-        <v>48</v>
-      </c>
-      <c r="C2" t="s">
-        <v>50</v>
-      </c>
-      <c r="D2" t="s">
-        <v>52</v>
-      </c>
-      <c r="E2" t="s">
-        <v>7</v>
-      </c>
-      <c r="F2" t="s">
-        <v>36</v>
-      </c>
-      <c r="G2">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7">
-      <c r="A3">
-        <v>23330051920303</v>
-      </c>
-      <c r="B3" t="s">
-        <v>49</v>
-      </c>
-      <c r="C3" t="s">
-        <v>51</v>
-      </c>
-      <c r="D3" t="s">
-        <v>53</v>
-      </c>
-      <c r="E3" t="s">
-        <v>7</v>
-      </c>
-      <c r="F3" t="s">
-        <v>36</v>
-      </c>
-      <c r="G3">
-        <v>5</v>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/grupos/3ASV - Estadisticos 20241.xlsx
+++ b/grupos/3ASV - Estadisticos 20241.xlsx
@@ -712,7 +712,7 @@
         <v>-1</v>
       </c>
       <c r="Q4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R4">
         <v>10</v>
@@ -801,7 +801,7 @@
         <v>-1</v>
       </c>
       <c r="Q5">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R5">
         <v>10</v>
@@ -890,7 +890,7 @@
         <v>-1</v>
       </c>
       <c r="Q6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R6">
         <v>10</v>
@@ -979,7 +979,7 @@
         <v>-1</v>
       </c>
       <c r="Q7">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R7">
         <v>10</v>
@@ -1068,7 +1068,7 @@
         <v>-1</v>
       </c>
       <c r="Q8">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R8">
         <v>10</v>
@@ -1157,7 +1157,7 @@
         <v>-1</v>
       </c>
       <c r="Q9">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R9">
         <v>10</v>
@@ -1178,7 +1178,7 @@
         <v>9</v>
       </c>
       <c r="X9">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="Y9">
         <v>9</v>
@@ -1246,7 +1246,7 @@
         <v>-1</v>
       </c>
       <c r="Q10">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R10">
         <v>10</v>
@@ -1267,7 +1267,7 @@
         <v>9</v>
       </c>
       <c r="X10">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Y10">
         <v>9</v>
@@ -1335,7 +1335,7 @@
         <v>-1</v>
       </c>
       <c r="Q11">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R11">
         <v>10</v>
@@ -1424,7 +1424,7 @@
         <v>-1</v>
       </c>
       <c r="Q12">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R12">
         <v>10</v>
@@ -1513,7 +1513,7 @@
         <v>-1</v>
       </c>
       <c r="Q13">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R13">
         <v>10</v>
@@ -1928,7 +1928,7 @@
         <v>100</v>
       </c>
       <c r="Q7">
-        <v>97.7</v>
+        <v>98.5</v>
       </c>
       <c r="R7">
         <v>97.90000000000001</v>
@@ -2064,7 +2064,7 @@
         <v>100</v>
       </c>
       <c r="Q9">
-        <v>93.2</v>
+        <v>95.5</v>
       </c>
       <c r="R9">
         <v>97.90000000000001</v>
@@ -2132,7 +2132,7 @@
         <v>100</v>
       </c>
       <c r="Q10">
-        <v>97.7</v>
+        <v>98.5</v>
       </c>
       <c r="R10">
         <v>97.90000000000001</v>
@@ -2200,7 +2200,7 @@
         <v>100</v>
       </c>
       <c r="Q11">
-        <v>97.7</v>
+        <v>98.5</v>
       </c>
       <c r="R11">
         <v>100</v>
@@ -2268,7 +2268,7 @@
         <v>100</v>
       </c>
       <c r="Q12">
-        <v>95.5</v>
+        <v>97</v>
       </c>
       <c r="R12">
         <v>91.7</v>
@@ -2336,7 +2336,7 @@
         <v>100</v>
       </c>
       <c r="Q13">
-        <v>97.7</v>
+        <v>98.5</v>
       </c>
       <c r="R13">
         <v>100</v>

--- a/grupos/3ASV - Estadisticos 20241.xlsx
+++ b/grupos/3ASV - Estadisticos 20241.xlsx
@@ -709,7 +709,7 @@
         <v>7</v>
       </c>
       <c r="P4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q4">
         <v>10</v>
@@ -724,7 +724,7 @@
         <v>6</v>
       </c>
       <c r="U4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V4">
         <v>10</v>
@@ -798,7 +798,7 @@
         <v>9</v>
       </c>
       <c r="P5">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q5">
         <v>10</v>
@@ -813,7 +813,7 @@
         <v>10</v>
       </c>
       <c r="U5">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V5">
         <v>10</v>
@@ -887,7 +887,7 @@
         <v>10</v>
       </c>
       <c r="P6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q6">
         <v>10</v>
@@ -902,7 +902,7 @@
         <v>10</v>
       </c>
       <c r="U6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V6">
         <v>10</v>
@@ -976,7 +976,7 @@
         <v>7</v>
       </c>
       <c r="P7">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q7">
         <v>9</v>
@@ -991,13 +991,13 @@
         <v>7</v>
       </c>
       <c r="U7">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="V7">
         <v>10</v>
       </c>
       <c r="W7">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="X7">
         <v>9</v>
@@ -1065,7 +1065,7 @@
         <v>9</v>
       </c>
       <c r="P8">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q8">
         <v>9</v>
@@ -1080,13 +1080,13 @@
         <v>7</v>
       </c>
       <c r="U8">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V8">
         <v>10</v>
       </c>
       <c r="W8">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="X8">
         <v>9</v>
@@ -1154,7 +1154,7 @@
         <v>10</v>
       </c>
       <c r="P9">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q9">
         <v>6</v>
@@ -1169,13 +1169,13 @@
         <v>6</v>
       </c>
       <c r="U9">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="V9">
         <v>10</v>
       </c>
       <c r="W9">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="X9">
         <v>8</v>
@@ -1243,7 +1243,7 @@
         <v>9</v>
       </c>
       <c r="P10">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q10">
         <v>10</v>
@@ -1258,13 +1258,13 @@
         <v>8</v>
       </c>
       <c r="U10">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V10">
         <v>10</v>
       </c>
       <c r="W10">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="X10">
         <v>9</v>
@@ -1332,7 +1332,7 @@
         <v>10</v>
       </c>
       <c r="P11">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q11">
         <v>10</v>
@@ -1347,7 +1347,7 @@
         <v>10</v>
       </c>
       <c r="U11">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V11">
         <v>10</v>
@@ -1421,7 +1421,7 @@
         <v>7</v>
       </c>
       <c r="P12">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q12">
         <v>9</v>
@@ -1436,7 +1436,7 @@
         <v>6</v>
       </c>
       <c r="U12">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="V12">
         <v>10</v>
@@ -1510,7 +1510,7 @@
         <v>9</v>
       </c>
       <c r="P13">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q13">
         <v>10</v>
@@ -1525,7 +1525,7 @@
         <v>9</v>
       </c>
       <c r="U13">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V13">
         <v>10</v>
@@ -1736,7 +1736,7 @@
         <v>100</v>
       </c>
       <c r="U4">
-        <v>98</v>
+        <v>98.8</v>
       </c>
       <c r="V4">
         <v>90.2</v>
@@ -1940,7 +1940,7 @@
         <v>98.40000000000001</v>
       </c>
       <c r="U7">
-        <v>98</v>
+        <v>97.5</v>
       </c>
       <c r="V7">
         <v>92</v>
@@ -2076,7 +2076,7 @@
         <v>98.40000000000001</v>
       </c>
       <c r="U9">
-        <v>100</v>
+        <v>97.5</v>
       </c>
       <c r="V9">
         <v>91.09999999999999</v>
@@ -2280,7 +2280,7 @@
         <v>100</v>
       </c>
       <c r="U12">
-        <v>98</v>
+        <v>97.5</v>
       </c>
       <c r="V12">
         <v>96.40000000000001</v>
@@ -2621,7 +2621,7 @@
         <v>0</v>
       </c>
       <c r="H8">
-        <v>9.300000000000001</v>
+        <v>8.9</v>
       </c>
       <c r="I8">
         <v>0</v>
